--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
@@ -12,8 +12,10 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Tabla_436729" sheetId="5" r:id="rId5"/>
+    <sheet name="Hidden_1_Tabla_436729" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="Hidden_1_Tabla_4367295">Hidden_1_Tabla_436729!$A$1:$A$2</definedName>
     <definedName name="Hidden_17">Hidden_1!$A$1:$A$4</definedName>
     <definedName name="Hidden_211">Hidden_2!$A$1:$A$2</definedName>
     <definedName name="Hidden_331">Hidden_3!$A$1:$A$7</definedName>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="130">
   <si>
     <t>48996</t>
   </si>
@@ -299,34 +301,34 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>687AE833703F83BA6BDBF9F097BD9D97</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>ver nota</t>
-  </si>
-  <si>
-    <t>4645386</t>
-  </si>
-  <si>
-    <t>Subdirección Juridica</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo por toda vez que no hay una recomendación emitida por la Comisión Estatal de Derechos Humanos</t>
+    <t>8497116</t>
+  </si>
+  <si>
+    <t>2AA3D40CA1AB5E14405724E8904A16F0</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>8101388</t>
+  </si>
+  <si>
+    <t>subdirección juridica</t>
+  </si>
+  <si>
+    <t>26/07/2023</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo, toda vez que no hay una recomendación emitida por la Comisión Nacional de Derechos Humanos; tal como lo establece el mismo reglamento interior de la comisión nacional en su capítulo VI.  fracciones I, II, III, IV, V, VI, VII, VIII, IX. en el que hace mención de las causas de conclusion.</t>
   </si>
   <si>
     <t>Recomendación específica</t>
@@ -377,6 +379,9 @@
     <t>56506</t>
   </si>
   <si>
+    <t>77790</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -387,6 +392,30 @@
   </si>
   <si>
     <t>Segundo apellido</t>
+  </si>
+  <si>
+    <t>Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t>DD4E0C9E6F1F547CABDC61C065279D04</t>
+  </si>
+  <si>
+    <t>Óscar</t>
+  </si>
+  <si>
+    <t>Lobatón</t>
+  </si>
+  <si>
+    <t>Corona</t>
+  </si>
+  <si>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -785,7 +814,7 @@
   <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -823,7 +852,7 @@
     <col min="36" max="36" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="20" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="202" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
@@ -1256,16 +1285,16 @@
     </row>
     <row r="8" spans="1:39" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>92</v>
@@ -1304,7 +1333,7 @@
         <v>92</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>92</v>
@@ -1316,7 +1345,7 @@
         <v>92</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>92</v>
@@ -1328,7 +1357,7 @@
         <v>92</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>92</v>
@@ -1337,7 +1366,7 @@
         <v>92</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>92</v>
@@ -1495,15 +1524,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="181.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -1513,8 +1545,11 @@
       <c r="E1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>114</v>
       </c>
@@ -1524,20 +1559,71 @@
       <c r="E2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+      <formula1>Hidden_1_Tabla_4367295</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
